--- a/Reliability/project1/Degradation_Fitting_Results.xlsx
+++ b/Reliability/project1/Degradation_Fitting_Results.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.865162460016179</v>
+        <v>1.865162459276827</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004623982316234901</v>
+        <v>0.0004623982318186424</v>
       </c>
       <c r="D2" t="n">
-        <v>3631.581651746446</v>
+        <v>3631.581651071032</v>
       </c>
       <c r="E2" t="n">
-        <v>0.002812903657101067</v>
+        <v>0.002812903683799761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9947627464940295</v>
+        <v>0.9947627453088127</v>
       </c>
       <c r="G2" t="n">
-        <v>3711.416778461581</v>
+        <v>3711.416779394289</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.733701261863151</v>
+        <v>1.733701257920153</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0004477594290203179</v>
+        <v>0.0004477594296942079</v>
       </c>
       <c r="D3" t="n">
-        <v>3913.544637071363</v>
+        <v>3913.544636260715</v>
       </c>
       <c r="E3" t="n">
-        <v>0.003260856607122557</v>
+        <v>0.003260856668242909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9614269575951988</v>
+        <v>0.9614269552505907</v>
       </c>
       <c r="G3" t="n">
-        <v>4232.096682567442</v>
+        <v>4232.096686242537</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.426750562352089</v>
+        <v>1.426750560870807</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0004149733214843902</v>
+        <v>0.00041497332186861</v>
       </c>
       <c r="D4" t="n">
-        <v>4692.315066051027</v>
+        <v>4692.315064208356</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005872282334885771</v>
+        <v>0.005872282412402585</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8503851481821602</v>
+        <v>0.850385146527327</v>
       </c>
       <c r="G4" t="n">
-        <v>6304.953956261123</v>
+        <v>6304.953965735248</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.361660129601174</v>
+        <v>1.361660129406929</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004082172832829162</v>
+        <v>0.0004082172831998529</v>
       </c>
       <c r="D5" t="n">
-        <v>4884.360696610535</v>
+        <v>4884.360697953849</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005902487164297909</v>
+        <v>0.005902487239152882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8419497655336609</v>
+        <v>0.8419497639400083</v>
       </c>
       <c r="G5" t="n">
-        <v>6840.755080548879</v>
+        <v>6840.755091851064</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.15000300537637</v>
+        <v>1.150003005480682</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004948279783553951</v>
+        <v>0.0004948279783545502</v>
       </c>
       <c r="D6" t="n">
-        <v>4370.853370983332</v>
+        <v>4370.853370807486</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0007687945535987214</v>
+        <v>0.0007687945280978228</v>
       </c>
       <c r="F6" t="n">
-        <v>1.109166818194049</v>
+        <v>1.109166822326526</v>
       </c>
       <c r="G6" t="n">
-        <v>5119.899468276411</v>
+        <v>5119.899458467201</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.828498793660225</v>
+        <v>1.828498797781268</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0004772084752823763</v>
+        <v>0.0004772084747231607</v>
       </c>
       <c r="D7" t="n">
-        <v>3560.476986760149</v>
+        <v>3560.476986209634</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001811919631285707</v>
+        <v>0.001811919623791593</v>
       </c>
       <c r="F7" t="n">
-        <v>1.053005781813955</v>
+        <v>1.053005782330099</v>
       </c>
       <c r="G7" t="n">
-        <v>3576.883300202609</v>
+        <v>3576.883299906384</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.024083846848348</v>
+        <v>1.024083850331754</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0004938532501103018</v>
+        <v>0.0004938532491102602</v>
       </c>
       <c r="D8" t="n">
-        <v>4614.299263054454</v>
+        <v>4614.299265510661</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0007589438820901387</v>
+        <v>0.0007589439164048682</v>
       </c>
       <c r="F8" t="n">
-        <v>1.095467087264711</v>
+        <v>1.095467081630149</v>
       </c>
       <c r="G8" t="n">
-        <v>5764.496753290549</v>
+        <v>5764.496772121346</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.127343358990699</v>
+        <v>1.127343356836156</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0004489806689833978</v>
+        <v>0.0004489806695491822</v>
       </c>
       <c r="D9" t="n">
-        <v>4861.50382135015</v>
+        <v>4861.503819480593</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002282149250157854</v>
+        <v>0.002282149341643174</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9522725192943975</v>
+        <v>0.9522725142791915</v>
       </c>
       <c r="G9" t="n">
-        <v>6670.742164737777</v>
+        <v>6670.742193276296</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.433359761606814</v>
+        <v>1.433359767932382</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0004467219979824527</v>
+        <v>0.0004467219965992454</v>
       </c>
       <c r="D10" t="n">
-        <v>4348.485030008733</v>
+        <v>4348.485033594299</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002970716197036302</v>
+        <v>0.002970716176571945</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9488314726629699</v>
+        <v>0.948831473524015</v>
       </c>
       <c r="G10" t="n">
-        <v>5216.151175006744</v>
+        <v>5216.151172360082</v>
       </c>
     </row>
     <row r="11">
@@ -685,22 +685,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.106980363022748</v>
+        <v>2.106980370767378</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000459845828935081</v>
+        <v>0.000459845827858896</v>
       </c>
       <c r="D11" t="n">
-        <v>3386.633476043942</v>
+        <v>3386.633475976405</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003292460543274763</v>
+        <v>0.003292460511038033</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9893290163537266</v>
+        <v>0.9893290175759838</v>
       </c>
       <c r="G11" t="n">
-        <v>3311.629393172535</v>
+        <v>3311.629392785726</v>
       </c>
     </row>
     <row r="12">
@@ -710,22 +710,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.397971927050639</v>
+        <v>1.397971925451504</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0004420523644158465</v>
+        <v>0.0004420523648079376</v>
       </c>
       <c r="D12" t="n">
-        <v>4450.971623639281</v>
+        <v>4450.971622279058</v>
       </c>
       <c r="E12" t="n">
-        <v>0.003100323337779091</v>
+        <v>0.003100323421569901</v>
       </c>
       <c r="F12" t="n">
-        <v>0.938591111505177</v>
+        <v>0.9385911081233137</v>
       </c>
       <c r="G12" t="n">
-        <v>5472.031119186264</v>
+        <v>5472.031131327891</v>
       </c>
     </row>
     <row r="13">
@@ -735,22 +735,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.511434943784405</v>
+        <v>1.511434950297338</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0004363775814504439</v>
+        <v>0.0004363775800622629</v>
       </c>
       <c r="D13" t="n">
-        <v>4330.024455502939</v>
+        <v>4330.024459402662</v>
       </c>
       <c r="E13" t="n">
-        <v>0.003901682013953032</v>
+        <v>0.003901682037325415</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9176266513316657</v>
+        <v>0.9176266505799791</v>
       </c>
       <c r="G13" t="n">
-        <v>5184.94356722559</v>
+        <v>5184.943569707387</v>
       </c>
     </row>
     <row r="14">
@@ -760,22 +760,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.406106038901214</v>
+        <v>1.406106042010752</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0004707723228403788</v>
+        <v>0.000470772322148337</v>
       </c>
       <c r="D14" t="n">
-        <v>4167.111761720817</v>
+        <v>4167.111763149028</v>
       </c>
       <c r="E14" t="n">
-        <v>0.001503397849103816</v>
+        <v>0.00150339775404466</v>
       </c>
       <c r="F14" t="n">
-        <v>1.041304962966092</v>
+        <v>1.04130497085505</v>
       </c>
       <c r="G14" t="n">
-        <v>4691.198747610136</v>
+        <v>4691.19873202549</v>
       </c>
     </row>
     <row r="15">
@@ -785,22 +785,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.095805983597146</v>
+        <v>1.09580598145779</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0004883075169766683</v>
+        <v>0.0004883075176329806</v>
       </c>
       <c r="D15" t="n">
-        <v>4528.078855090692</v>
+        <v>4528.078853002824</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0007752318559703347</v>
+        <v>0.0007752318380900422</v>
       </c>
       <c r="F15" t="n">
-        <v>1.099545993709199</v>
+        <v>1.099545996583873</v>
       </c>
       <c r="G15" t="n">
-        <v>5475.494218307637</v>
+        <v>5475.494209937322</v>
       </c>
     </row>
     <row r="16">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.107057695677987</v>
+        <v>1.1070576977104</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0004694061669867694</v>
+        <v>0.000469406166389271</v>
       </c>
       <c r="D16" t="n">
-        <v>4688.645945585585</v>
+        <v>4688.645947642631</v>
       </c>
       <c r="E16" t="n">
-        <v>0.001320898848311963</v>
+        <v>0.001320898854772036</v>
       </c>
       <c r="F16" t="n">
-        <v>1.026587545745712</v>
+        <v>1.026587545135875</v>
       </c>
       <c r="G16" t="n">
-        <v>6007.102046900913</v>
+        <v>6007.102049331298</v>
       </c>
     </row>
   </sheetData>
